--- a/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
+++ b/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,7%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 48,6%</t>
+        <v>4</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 39,7%</t>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,9%</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 412,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 236,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3600,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 48,6%</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1182,24 +1182,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 39,7%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 412,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1401,24 +1401,24 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>58</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 236,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,24 +1474,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>37</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3600,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1695,9 +1695,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1760,17 +1760,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 90,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2276,51 +2276,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2345,12 +2341,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
@@ -2358,20 +2354,20 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2388,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2427,11 +2423,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2461,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2491,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2534,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2573,11 +2569,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2637,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2680,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2710,7 +2706,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2718,8 +2714,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>2</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2728,37 +2726,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2792,24 +2792,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2864,10 +2864,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2876,39 +2874,37 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2942,11 +2938,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,12 +2972,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3017,9 +3013,9 @@
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3049,12 +3045,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3079,25 +3075,25 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 255,6%</t>
+        <v>5</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -3105,7 +3101,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3122,12 +3118,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3161,11 +3157,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3183,7 +3179,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3195,12 +3191,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3225,7 +3221,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3234,24 +3230,24 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3268,12 +3264,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3298,7 +3294,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3306,47 +3302,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3374,17 +3374,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3487,12 +3487,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3517,33 +3517,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>32</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 255,6%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3663,33 +3663,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 280,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3747,9 +3747,9 @@
       <c r="I45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3809,33 +3809,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3852,12 +3852,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3891,11 +3891,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3955,33 +3955,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4031,17 +4031,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4101,33 +4101,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 280,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▲ 2700,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4183,24 +4183,24 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4247,33 +4247,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4331,9 +4331,9 @@
       <c r="I53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4363,12 +4363,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4396,22 +4396,22 @@
           <t>R$ 70,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4469,13 +4469,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4509,12 +4509,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4539,33 +4539,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>28</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2700,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4621,29 +4621,29 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4685,33 +4685,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4767,11 +4767,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4831,33 +4831,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4913,11 +4913,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4947,12 +4947,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4977,33 +4977,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 172,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 89,9%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5123,33 +5123,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 516,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 125,3%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>198</v>
+        <v>8</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 52,2%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5205,11 +5205,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5269,33 +5269,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>414</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 107,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5350,51 +5350,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I67" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5419,33 +5415,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 344,00</t>
+          <t>R$ 172,00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,1%</t>
+          <t>▼ 89,9%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5462,12 +5458,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5492,7 +5488,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5500,51 +5496,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5569,33 +5561,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
+          <t>R$ 516,00</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,4%</t>
+          <t>▲ 125,3%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>213</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,5%</t>
+        <v>198</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 52,2%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5612,12 +5604,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5642,7 +5634,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5650,10 +5642,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5662,39 +5652,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5724,20 +5712,20 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,3%</t>
+        <v>414</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 107,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5745,7 +5733,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5762,12 +5750,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5839,12 +5827,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5869,33 +5857,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 401,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,6%</t>
+          <t>R$ 344,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>222</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,3%</t>
+        <v>200</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5912,12 +5900,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5989,12 +5977,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6019,25 +6007,25 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 387,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,4%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>213</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,5%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6045,7 +6033,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6062,82 +6050,532 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,3%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 401,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,6%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,3%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-032</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Petala Jasmin -1730</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 387,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>4533595417</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,90</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
+++ b/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,8 +597,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -607,39 +609,41 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -662,33 +666,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +750,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +782,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -808,33 +812,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -890,11 +894,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +928,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -954,33 +958,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +1001,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1030,17 +1034,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,14 +1074,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1100,20 +1104,20 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 48,6%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1122,11 +1126,11 @@
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1147,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1173,33 +1177,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1220,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1246,33 +1250,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,0%</t>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 39,7%</t>
+          <t>▼ 48,6%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1293,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1319,33 +1323,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,9%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1366,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1392,33 +1396,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 412,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>35</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 39,7%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1439,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1465,33 +1469,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 236,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3600,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1512,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1538,7 +1542,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 412,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1547,24 +1551,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>58</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1585,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1611,7 +1615,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 236,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1620,24 +1624,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>37</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3600,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1658,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1693,11 +1697,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,14 +1731,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1760,17 +1764,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,14 +1804,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1839,11 +1843,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,14 +1877,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1903,33 +1907,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1950,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1989,7 +1993,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,14 +2023,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2049,7 +2053,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2058,24 +2062,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2096,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2131,7 +2135,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2165,14 +2169,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2204,11 +2208,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2279,9 +2283,9 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,14 +2315,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2344,17 +2348,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,14 +2388,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2423,11 +2427,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,14 +2461,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2487,33 +2491,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2534,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2573,7 +2577,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,14 +2607,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2633,25 +2637,25 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 177,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2659,7 +2663,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2680,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2706,7 +2710,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2714,10 +2718,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2726,41 +2728,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2783,33 +2783,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2826,14 +2826,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2864,8 +2864,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2874,39 +2876,41 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2929,33 +2933,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2972,12 +2976,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3013,9 +3017,9 @@
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3045,14 +3049,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3075,33 +3079,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3118,14 +3122,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3157,11 +3161,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3191,14 +3195,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3221,7 +3225,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3230,24 +3234,24 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3264,14 +3268,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3294,7 +3298,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3302,10 +3306,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3314,41 +3316,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3374,17 +3374,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3414,14 +3414,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3452,8 +3452,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3462,39 +3464,41 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3517,33 +3521,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 255,6%</t>
+        <v>4</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3560,12 +3564,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3601,9 +3605,9 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3621,7 +3625,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3633,14 +3637,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3663,25 +3667,25 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 255,6%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3689,7 +3693,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3706,14 +3710,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3745,11 +3749,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3767,7 +3771,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3779,14 +3783,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3809,7 +3813,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3818,24 +3822,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3852,14 +3856,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3891,11 +3895,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3925,14 +3929,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3958,17 +3962,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3998,14 +4002,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4037,11 +4041,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4071,14 +4075,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4101,33 +4105,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 280,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4144,14 +4148,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4183,11 +4187,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4217,14 +4221,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4247,33 +4251,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
+          <t>R$ 280,00</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>80,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4290,12 +4294,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4331,9 +4335,9 @@
       <c r="I53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4363,14 +4367,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4393,33 +4397,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4436,14 +4440,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4469,17 +4473,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4509,14 +4513,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4539,33 +4543,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2700,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4582,14 +4586,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4612,33 +4616,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4655,14 +4659,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4685,33 +4689,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
+        <v>28</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2700,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4728,14 +4732,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4758,7 +4762,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4767,24 +4771,24 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4801,14 +4805,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4831,33 +4835,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4874,12 +4878,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4947,14 +4951,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4977,33 +4981,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5020,12 +5024,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5063,7 +5067,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5081,7 +5085,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5093,14 +5097,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5123,33 +5127,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5166,14 +5170,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5205,11 +5209,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5227,7 +5231,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5239,14 +5243,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5269,33 +5273,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5312,14 +5316,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5351,11 +5355,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5385,14 +5389,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5415,33 +5419,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 172,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 89,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5458,14 +5462,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5497,11 +5501,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5531,14 +5535,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5561,33 +5565,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 516,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 125,3%</t>
+          <t>R$ 172,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 52,2%</t>
+          <t>▼ 89,9%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5604,12 +5608,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5647,7 +5651,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5665,7 +5669,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5677,14 +5681,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5707,33 +5711,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,4%</t>
+          <t>R$ 516,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 125,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>414</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 107,0%</t>
+        <v>198</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 52,2%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5750,14 +5754,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5780,7 +5784,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5788,10 +5792,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5800,41 +5802,39 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5857,25 +5857,25 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 344,00</t>
+          <t>R$ 229,00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,1%</t>
+        <v>414</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 107,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5977,14 +5977,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6007,33 +6007,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,4%</t>
+          <t>R$ 344,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>213</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,5%</t>
+        <v>200</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6127,14 +6127,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6157,33 +6157,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,4%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,3%</t>
+        <v>213</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,5%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6277,14 +6277,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6307,33 +6307,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 401,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,6%</t>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>222</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,3%</t>
+        <v>137</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,3%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6427,14 +6427,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6457,20 +6457,20 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 387,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 401,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,6%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>222</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6500,82 +6500,232 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-032</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Petala Jasmin -1730</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 387,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>4533595417</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,90</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
+++ b/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,33 +666,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,8 +747,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -757,37 +759,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -812,7 +816,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -821,24 +825,24 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -855,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -885,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -893,47 +897,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -961,17 +969,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1001,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1031,7 +1039,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1039,47 +1047,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1104,33 +1116,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1147,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1180,17 +1192,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1220,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1250,33 +1262,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,7%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 48,6%</t>
+        <v>4</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1293,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1323,7 +1335,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1332,24 +1344,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1366,12 +1378,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1396,33 +1408,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 39,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1439,12 +1451,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1472,9 +1484,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
@@ -1482,7 +1494,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 91,9%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1512,12 +1524,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1542,33 +1554,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 412,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▲ 2800,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1585,12 +1597,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1615,33 +1627,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 236,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 3600,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1658,12 +1670,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1688,33 +1700,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 48,6%</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1731,12 +1743,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1761,7 +1773,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1770,24 +1782,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1804,12 +1816,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1834,33 +1846,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>35</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 39,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1877,12 +1889,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1910,17 +1922,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1950,12 +1962,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1980,7 +1992,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 412,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1989,24 +2001,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>58</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2023,12 +2035,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2053,7 +2065,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 236,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2062,24 +2074,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 3600,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2096,12 +2108,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2135,7 +2147,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2169,12 +2181,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2208,11 +2220,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2242,12 +2254,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2283,9 +2295,9 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2315,12 +2327,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2348,17 +2360,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2388,12 +2400,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2427,11 +2439,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2461,12 +2473,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2491,33 +2503,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2534,12 +2546,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2577,7 +2589,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,12 +2619,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2637,33 +2649,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▲ 233,3%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2680,12 +2692,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2719,7 +2731,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2753,12 +2765,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2783,33 +2795,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2826,12 +2838,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2856,7 +2868,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2864,51 +2876,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2933,33 +2941,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2976,12 +2984,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3015,11 +3023,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3049,12 +3057,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3079,33 +3087,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 177,00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3122,12 +3130,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3161,11 +3169,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3195,12 +3203,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3225,33 +3233,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3268,12 +3276,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3298,7 +3306,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3306,8 +3314,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>2</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3316,37 +3326,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3371,7 +3383,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3380,24 +3392,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3414,12 +3426,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3444,7 +3456,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3452,10 +3464,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3464,39 +3474,37 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3524,17 +3532,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>3</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3564,12 +3572,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3605,9 +3613,9 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3637,12 +3645,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3667,25 +3675,25 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▲ 255,6%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3693,7 +3701,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3710,12 +3718,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3749,11 +3757,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3771,7 +3779,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3783,12 +3791,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3813,7 +3821,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3822,24 +3830,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3856,12 +3864,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3886,7 +3894,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3894,47 +3902,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3962,17 +3974,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4002,12 +4014,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4041,7 +4053,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4075,12 +4087,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4105,33 +4117,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 140,00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 255,6%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4148,12 +4160,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4189,7 +4201,7 @@
       <c r="I51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -4209,7 +4221,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4221,12 +4233,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4251,33 +4263,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 280,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4294,12 +4306,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4335,9 +4347,9 @@
       <c r="I53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4367,12 +4379,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4397,33 +4409,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4440,12 +4452,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4479,11 +4491,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4513,12 +4525,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4543,33 +4555,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4586,12 +4598,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4619,17 +4631,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4659,12 +4671,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4689,33 +4701,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 280,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2700,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4732,12 +4744,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4762,7 +4774,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4771,24 +4783,24 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4805,12 +4817,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4835,33 +4847,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 210,00</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
+        <v>4</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4878,12 +4890,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4919,9 +4931,9 @@
       <c r="I61" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4951,12 +4963,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4984,22 +4996,22 @@
           <t>R$ 70,00</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -5007,7 +5019,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5024,12 +5036,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5057,13 +5069,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5097,12 +5109,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5127,33 +5139,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 2700,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5170,12 +5182,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5200,7 +5212,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5209,29 +5221,29 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5243,12 +5255,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5273,33 +5285,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5316,12 +5328,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5355,11 +5367,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5389,12 +5401,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5419,33 +5431,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5462,12 +5474,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5501,11 +5513,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5535,12 +5547,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5565,33 +5577,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 172,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 89,9%</t>
+        <v>6</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5608,12 +5620,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5651,7 +5663,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5669,7 +5681,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5681,12 +5693,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5711,33 +5723,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 516,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 125,3%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 52,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5754,12 +5766,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5793,11 +5805,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5815,7 +5827,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5827,12 +5839,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5857,33 +5869,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>414</v>
+        <v>10</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 107,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5900,12 +5912,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5930,7 +5942,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5938,51 +5950,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I75" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6007,33 +6015,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 344,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 172,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,1%</t>
+        <v>20</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 89,9%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6050,12 +6058,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6080,7 +6088,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6088,51 +6096,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6157,33 +6161,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,4%</t>
+          <t>R$ 516,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 125,3%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 55,5%</t>
+          <t>▼ 52,2%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6200,12 +6204,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6230,7 +6234,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6238,10 +6242,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6250,39 +6252,37 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6310,22 +6310,22 @@
           <t>R$ 229,00</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>137</v>
+        <v>414</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 38,3%</t>
+          <t>▲ 107,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6457,33 +6457,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 401,00</t>
+          <t>R$ 344,00</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,6%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,3%</t>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6500,12 +6500,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6607,25 +6607,25 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 387,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,4%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>213</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 55,5%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6650,82 +6650,532 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 38,3%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 401,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,6%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,3%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-032</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Petala Jasmin -1730</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 387,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>4533595417</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,90</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
+++ b/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,20 +671,20 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▼ 68,4%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -692,7 +692,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,10 +747,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -759,39 +757,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -816,33 +812,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,6%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -859,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -966,33 +962,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 3,8%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1009,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1086,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1116,33 +1112,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1159,12 +1155,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,7 +1185,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1197,8 +1193,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1207,37 +1205,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1271,24 +1271,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1343,47 +1343,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1411,17 +1415,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1451,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1481,7 +1485,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1489,47 +1493,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1554,33 +1562,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1597,12 +1605,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1630,17 +1638,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1670,12 +1678,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1700,33 +1708,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,7%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 48,6%</t>
+        <v>4</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1743,12 +1751,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1773,7 +1781,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1782,24 +1790,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1816,12 +1824,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1846,33 +1854,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 39,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1889,12 +1897,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1922,9 +1930,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
@@ -1932,7 +1940,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▼ 91,9%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1962,12 +1970,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1992,33 +2000,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 412,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▲ 2800,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2035,12 +2043,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2065,33 +2073,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 236,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 3600,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2108,12 +2116,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2138,33 +2146,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 48,6%</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2181,12 +2189,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2211,7 +2219,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2220,24 +2228,24 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2254,12 +2262,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2284,33 +2292,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>35</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 39,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2327,12 +2335,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2360,17 +2368,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2400,12 +2408,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2430,7 +2438,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 412,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2439,24 +2447,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>58</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2473,12 +2481,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2503,7 +2511,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 236,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2512,24 +2520,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 3600,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2546,12 +2554,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2585,7 +2593,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2619,12 +2627,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2658,11 +2666,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2692,12 +2700,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2733,9 +2741,9 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2765,12 +2773,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2798,17 +2806,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2838,12 +2846,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2877,11 +2885,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2911,12 +2919,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2941,33 +2949,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 90,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2984,12 +2992,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3027,7 +3035,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3057,12 +3065,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3087,33 +3095,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▲ 233,3%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3130,12 +3138,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3169,7 +3177,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3203,12 +3211,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3233,33 +3241,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3276,12 +3284,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3306,7 +3314,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3314,51 +3322,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3383,33 +3387,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3426,12 +3430,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3465,11 +3469,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3499,12 +3503,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3529,33 +3533,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 177,00</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3572,12 +3576,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3611,11 +3615,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3645,12 +3649,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3675,33 +3679,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3718,12 +3722,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3748,7 +3752,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3756,8 +3760,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>2</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3766,37 +3772,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3821,7 +3829,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3830,24 +3838,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3864,12 +3872,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3894,7 +3902,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3902,10 +3910,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3914,39 +3920,37 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3974,17 +3978,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4014,12 +4018,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4055,9 +4059,9 @@
       <c r="I49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4087,12 +4091,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4117,25 +4121,25 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▲ 255,6%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -4143,7 +4147,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4160,12 +4164,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4199,11 +4203,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4221,7 +4225,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4233,12 +4237,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4263,7 +4267,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4272,24 +4276,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4306,12 +4310,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4336,7 +4340,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4344,47 +4348,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4412,17 +4420,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4452,12 +4460,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4491,7 +4499,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4525,12 +4533,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4555,33 +4563,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 140,00</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 255,6%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4598,12 +4606,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4639,7 +4647,7 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -4659,7 +4667,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4671,12 +4679,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4701,33 +4709,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 280,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4744,12 +4752,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4785,9 +4793,9 @@
       <c r="I59" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4817,12 +4825,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4847,33 +4855,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4890,12 +4898,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4929,11 +4937,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4963,12 +4971,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4993,33 +5001,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5036,12 +5044,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5069,17 +5077,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5109,12 +5117,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5139,33 +5147,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 280,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2700,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5182,12 +5190,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5212,7 +5220,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5221,24 +5229,24 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5255,12 +5263,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5285,33 +5293,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 210,00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
+        <v>4</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5328,12 +5336,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5369,9 +5377,9 @@
       <c r="I67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5401,12 +5409,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5434,22 +5442,22 @@
           <t>R$ 70,00</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5457,7 +5465,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5474,12 +5482,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5507,13 +5515,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5547,12 +5555,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5577,33 +5585,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 2700,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5620,12 +5628,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5650,7 +5658,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5659,29 +5667,29 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5693,12 +5701,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5723,33 +5731,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5766,12 +5774,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5805,11 +5813,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5839,12 +5847,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5869,33 +5877,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5912,12 +5920,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5951,11 +5959,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5985,12 +5993,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6015,33 +6023,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 172,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 89,9%</t>
+        <v>6</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6058,12 +6066,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6101,7 +6109,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6119,7 +6127,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6131,12 +6139,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6161,33 +6169,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 516,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▲ 125,3%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 52,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6204,12 +6212,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6243,11 +6251,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6265,7 +6273,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6277,12 +6285,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6307,33 +6315,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>414</v>
+        <v>10</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▲ 107,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6350,12 +6358,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6380,7 +6388,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6388,51 +6396,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I81" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6457,33 +6461,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 344,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 172,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,1%</t>
+        <v>20</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 89,9%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6500,12 +6504,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6530,7 +6534,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6538,51 +6542,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6607,33 +6607,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,4%</t>
+          <t>R$ 516,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 125,3%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▲ 55,5%</t>
+          <t>▼ 52,2%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6650,12 +6650,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6688,10 +6688,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6700,39 +6698,37 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6760,22 +6756,22 @@
           <t>R$ 229,00</t>
         </is>
       </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>137</v>
+        <v>414</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▼ 38,3%</t>
+          <t>▲ 107,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6783,7 +6779,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6800,12 +6796,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6877,12 +6873,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6907,33 +6903,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 401,00</t>
+          <t>R$ 344,00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,6%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▲ 2,3%</t>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6950,12 +6946,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7027,12 +7023,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7057,25 +7053,25 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 387,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,4%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>213</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,5%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
@@ -7083,7 +7079,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7100,82 +7096,532 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,3%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 401,00</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,6%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,3%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-032</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Petala Jasmin -1730</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 387,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>4533595417</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,90</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
+++ b/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,14 +636,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 68,4%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -692,7 +692,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,8 +747,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -757,39 +759,41 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -815,22 +819,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 29,6%</t>
+          <t>▼ 68,4%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -855,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -885,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -893,10 +897,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -905,41 +907,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -962,33 +962,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,8%</t>
+        <v>19</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,6%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1005,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1082,14 +1082,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1112,33 +1112,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▲ 3,8%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1232,14 +1232,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1271,24 +1271,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>26</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1382,14 +1382,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1421,11 +1421,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1455,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1532,14 +1532,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1565,17 +1565,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1605,14 +1605,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1643,8 +1643,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1653,39 +1655,41 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1708,33 +1712,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1751,12 +1755,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1792,9 +1796,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1824,14 +1828,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1854,33 +1858,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1897,14 +1901,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1936,11 +1940,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1970,14 +1974,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2000,33 +2004,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2043,14 +2047,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2076,17 +2080,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2116,14 +2120,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2146,20 +2150,20 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▼ 48,6%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2168,11 +2172,11 @@
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2189,14 +2193,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2219,33 +2223,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2262,14 +2266,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2292,33 +2296,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,0%</t>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 39,7%</t>
+          <t>▼ 48,6%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2335,14 +2339,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2365,33 +2369,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,9%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2408,14 +2412,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2438,33 +2442,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 412,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>35</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 39,7%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2481,14 +2485,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2511,33 +2515,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 236,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3600,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2554,14 +2558,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2584,7 +2588,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 412,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2593,24 +2597,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>58</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2627,14 +2631,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2657,7 +2661,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 236,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2666,24 +2670,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>37</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3600,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2700,14 +2704,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2739,11 +2743,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2773,14 +2777,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2806,17 +2810,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2846,14 +2850,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2885,11 +2889,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2919,14 +2923,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2949,33 +2953,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2992,12 +2996,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3035,7 +3039,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3065,14 +3069,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3095,7 +3099,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3104,24 +3108,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3138,14 +3142,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3177,7 +3181,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3211,14 +3215,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3250,11 +3254,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3284,12 +3288,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3325,9 +3329,9 @@
       <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3357,14 +3361,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3390,17 +3394,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3430,14 +3434,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3469,11 +3473,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3503,14 +3507,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3533,33 +3537,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3576,12 +3580,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3619,7 +3623,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3649,14 +3653,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3679,25 +3683,25 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 177,00</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3705,7 +3709,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3722,14 +3726,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3752,7 +3756,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3760,10 +3764,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3772,41 +3774,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3829,33 +3829,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3872,14 +3872,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3910,8 +3910,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3920,39 +3922,41 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3975,33 +3979,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4018,12 +4022,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4059,9 +4063,9 @@
       <c r="I49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4091,14 +4095,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4121,33 +4125,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4164,14 +4168,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4203,11 +4207,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4237,14 +4241,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4267,7 +4271,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4276,24 +4280,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4310,14 +4314,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4340,7 +4344,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4348,10 +4352,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4360,41 +4362,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4420,17 +4420,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4460,14 +4460,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4498,8 +4498,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4508,39 +4510,41 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4563,33 +4567,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 255,6%</t>
+        <v>4</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4606,12 +4610,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4647,9 +4651,9 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4667,7 +4671,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4679,14 +4683,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4709,25 +4713,25 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 255,6%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -4735,7 +4739,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4752,14 +4756,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4791,11 +4795,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4813,7 +4817,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4825,14 +4829,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4855,7 +4859,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4864,24 +4868,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4898,14 +4902,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4937,11 +4941,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4971,14 +4975,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5004,17 +5008,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5044,14 +5048,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5083,11 +5087,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5117,14 +5121,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5147,33 +5151,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 280,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5190,14 +5194,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5229,11 +5233,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5263,14 +5267,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5293,33 +5297,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
+          <t>R$ 280,00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>80,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5336,12 +5340,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5377,9 +5381,9 @@
       <c r="I67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5409,14 +5413,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5439,33 +5443,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
-        </is>
-      </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5482,14 +5486,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5515,17 +5519,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5555,14 +5559,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5585,33 +5589,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2700,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5628,14 +5632,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5658,33 +5662,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5701,14 +5705,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5731,33 +5735,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
+        <v>28</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2700,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5774,14 +5778,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5804,7 +5808,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5813,24 +5817,24 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5847,14 +5851,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5877,33 +5881,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5920,12 +5924,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5993,14 +5997,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6023,33 +6027,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6066,12 +6070,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6109,7 +6113,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6127,7 +6131,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6139,14 +6143,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6169,33 +6173,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6212,14 +6216,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6251,11 +6255,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6273,7 +6277,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6285,14 +6289,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6315,33 +6319,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6358,14 +6362,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6397,11 +6401,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6431,14 +6435,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6461,33 +6465,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 172,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 89,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6504,14 +6508,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6543,11 +6547,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6577,14 +6581,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6607,33 +6611,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 516,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 125,3%</t>
+          <t>R$ 172,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 52,2%</t>
+          <t>▼ 89,9%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6650,12 +6654,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6693,7 +6697,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6711,7 +6715,7 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -6723,14 +6727,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6753,33 +6757,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,4%</t>
+          <t>R$ 516,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 125,3%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>414</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 107,0%</t>
+        <v>198</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 52,2%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6796,14 +6800,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6826,7 +6830,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6834,10 +6838,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6846,41 +6848,39 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6903,25 +6903,25 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 344,00</t>
+          <t>R$ 229,00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,1%</t>
+        <v>414</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 107,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7023,14 +7023,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7053,33 +7053,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,4%</t>
+          <t>R$ 344,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>213</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,5%</t>
+        <v>200</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7173,14 +7173,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7203,33 +7203,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,4%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,3%</t>
+        <v>213</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,5%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7246,12 +7246,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7323,14 +7323,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7353,33 +7353,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 401,00</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,6%</t>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>222</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,3%</t>
+        <v>137</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,3%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7396,12 +7396,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7473,14 +7473,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7503,20 +7503,20 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 387,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 401,00</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,6%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>222</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,3%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7546,82 +7546,232 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-032</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Petala Jasmin -1730</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 387,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>4533595417</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,90</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
+++ b/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -669,22 +669,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -692,7 +692,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -816,33 +816,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 68,4%</t>
+        <v>10</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -897,8 +897,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -907,37 +909,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -965,22 +969,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 29,6%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -988,7 +992,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1005,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1082,12 +1086,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1112,33 +1116,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,8%</t>
+        <v>6</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,4%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1155,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1185,7 +1189,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1193,10 +1197,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1205,39 +1207,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1265,22 +1265,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>19</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,6%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1412,33 +1412,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>27</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,8%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1455,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1571,24 +1571,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1605,12 +1605,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1715,17 +1715,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1793,8 +1793,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1803,37 +1805,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1858,7 +1862,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1867,24 +1871,24 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1901,12 +1905,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1931,7 +1935,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1939,47 +1943,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2013,11 +2021,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+        <v>7</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2047,12 +2055,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2086,11 +2094,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2120,12 +2128,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2153,22 +2161,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
@@ -2176,7 +2184,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2193,12 +2201,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2226,17 +2234,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2266,12 +2274,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2296,33 +2304,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 48,6%</t>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2339,12 +2347,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2369,7 +2377,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2380,22 +2388,22 @@
       <c r="I26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2412,12 +2420,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2442,33 +2450,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 39,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2485,12 +2493,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2524,11 +2532,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 91,9%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2558,12 +2566,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2588,33 +2596,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 412,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 48,6%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2631,12 +2639,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2661,7 +2669,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 236,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2670,24 +2678,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3600,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2704,12 +2712,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2734,33 +2742,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>35</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 39,7%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2777,12 +2785,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2810,17 +2818,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2850,12 +2858,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2880,7 +2888,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 412,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2889,24 +2897,24 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>58</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2923,12 +2931,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2953,33 +2961,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 236,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 3600,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2996,12 +3004,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3035,11 +3043,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3069,12 +3077,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3099,7 +3107,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3112,20 +3120,20 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3142,12 +3150,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3181,11 +3189,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3215,12 +3223,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3248,17 +3256,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3288,12 +3296,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3327,11 +3335,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3361,12 +3369,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3391,7 +3399,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3400,24 +3408,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3434,12 +3442,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3473,11 +3481,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3507,12 +3515,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3540,17 +3548,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 90,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3580,12 +3588,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3619,11 +3627,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3653,12 +3661,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3683,33 +3691,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▲ 233,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3726,12 +3734,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3765,11 +3773,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3799,12 +3807,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3829,33 +3837,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3872,12 +3880,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3902,7 +3910,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3910,51 +3918,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3979,33 +3983,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4022,12 +4026,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4061,7 +4065,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4095,12 +4099,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4125,33 +4129,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4168,12 +4172,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4198,7 +4202,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4206,47 +4210,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4280,16 +4288,16 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -4297,7 +4305,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4314,12 +4322,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4353,7 +4361,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4387,12 +4395,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4420,17 +4428,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4460,12 +4468,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4490,7 +4498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4498,51 +4506,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4567,33 +4571,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4610,12 +4614,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4649,7 +4653,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4683,12 +4687,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4713,33 +4717,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 255,6%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4756,12 +4760,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4786,7 +4790,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4794,47 +4798,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4859,33 +4867,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4902,12 +4910,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4941,11 +4949,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4975,12 +4983,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5005,33 +5013,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>32</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 255,6%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5048,12 +5056,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5087,11 +5095,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5109,7 +5117,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5121,12 +5129,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5151,33 +5159,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5194,12 +5202,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5233,11 +5241,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5267,12 +5275,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5297,33 +5305,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 280,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5340,12 +5348,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5379,11 +5387,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5413,12 +5421,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5443,33 +5451,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5486,12 +5494,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5525,11 +5533,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5559,12 +5567,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5589,33 +5597,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 280,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>5</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5632,12 +5640,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5665,13 +5673,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5705,12 +5713,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5735,33 +5743,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2700,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5778,12 +5786,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5808,7 +5816,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5817,24 +5825,24 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5851,12 +5859,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5881,33 +5889,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5924,12 +5932,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5957,13 +5965,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -5997,12 +6005,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6027,7 +6035,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 140,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6036,24 +6044,24 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 2700,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6070,12 +6078,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6100,7 +6108,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6109,24 +6117,24 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6143,12 +6151,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6182,11 +6190,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6216,12 +6224,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6259,7 +6267,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6277,7 +6285,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6289,12 +6297,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6319,7 +6327,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6328,24 +6336,24 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6362,12 +6370,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6401,11 +6409,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6435,12 +6443,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6474,11 +6482,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6508,12 +6516,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6547,11 +6555,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6569,7 +6577,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -6581,12 +6589,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6611,25 +6619,25 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 172,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 89,9%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
@@ -6637,7 +6645,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6654,12 +6662,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6693,11 +6701,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6727,12 +6735,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6757,33 +6765,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 516,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 125,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>198</v>
+        <v>10</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 52,2%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6800,12 +6808,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6839,11 +6847,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6861,7 +6869,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6873,12 +6881,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6903,33 +6911,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
+          <t>R$ 172,00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,4%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>414</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 107,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 89,9%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6946,12 +6954,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6976,7 +6984,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6984,51 +6992,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I89" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7053,33 +7057,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 344,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 516,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 125,3%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,1%</t>
+          <t>▼ 52,2%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7096,12 +7100,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7126,7 +7130,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7134,10 +7138,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7146,39 +7148,37 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7203,33 +7203,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,4%</t>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>213</v>
+        <v>414</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▲ 55,5%</t>
+          <t>▲ 107,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7246,12 +7246,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7353,25 +7353,25 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
+          <t>R$ 344,00</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 38,3%</t>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7396,12 +7396,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7473,12 +7473,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7503,25 +7503,25 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 401,00</t>
+          <t>R$ 459,00</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,6%</t>
+          <t>▲ 100,4%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,3%</t>
+          <t>▲ 55,5%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7546,12 +7546,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7653,33 +7653,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 387,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>137</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,3%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7696,82 +7696,382 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 401,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,6%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,3%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-032</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Petala Jasmin -1730</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 387,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>4533595417</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,90</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
+++ b/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,33 +666,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -816,33 +816,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,12 +936,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -966,33 +966,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1125,16 +1125,16 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 68,4%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1197,8 +1197,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1207,37 +1209,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1265,22 +1269,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 29,6%</t>
+          <t>▼ 61,5%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -1288,7 +1292,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1305,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1382,12 +1386,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1412,33 +1416,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,8%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1455,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1532,12 +1536,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1562,7 +1566,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1571,24 +1575,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1605,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1682,12 +1686,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1715,17 +1719,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 81,2%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1755,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1832,12 +1836,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1862,33 +1866,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1982,12 +1986,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2012,33 +2016,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2055,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2128,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2158,33 +2162,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>13</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2201,12 +2205,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2231,7 +2235,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2239,47 +2243,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2304,33 +2312,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+        <v>11</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2347,12 +2355,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2377,7 +2385,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2385,47 +2393,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2459,16 +2471,16 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -2493,12 +2505,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2523,55 +2535,59 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2599,22 +2615,22 @@
           <t>R$ 158,00</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,7%</t>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 48,6%</t>
+        <v>10</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
@@ -2622,7 +2638,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2639,12 +2655,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2669,7 +2685,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2677,47 +2693,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>3</v>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2742,33 +2762,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 39,7%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2785,12 +2805,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2815,55 +2835,59 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,9%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2888,33 +2912,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 412,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,4%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2931,12 +2955,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2961,7 +2985,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 236,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2970,24 +2994,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3600,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3004,12 +3028,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3034,33 +3058,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,6%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3077,12 +3101,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3107,7 +3131,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3115,47 +3139,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3180,33 +3208,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>27</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,8%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3223,12 +3251,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3253,55 +3281,59 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3326,7 +3358,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3335,24 +3367,24 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3369,12 +3401,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3399,7 +3431,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3407,47 +3439,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3481,7 +3517,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3515,12 +3551,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3545,7 +3581,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3553,47 +3589,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3629,9 +3669,9 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3661,12 +3701,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3691,7 +3731,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3699,47 +3739,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3767,17 +3811,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3807,12 +3851,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3840,17 +3884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3880,12 +3924,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3910,7 +3954,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3919,24 +3963,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3953,12 +3997,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3983,33 +4027,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4026,12 +4070,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4059,17 +4103,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4099,12 +4143,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4129,16 +4173,16 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -4147,15 +4191,15 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4172,12 +4216,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4202,59 +4246,55 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4279,33 +4319,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4322,12 +4362,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4352,33 +4392,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>18</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 48,6%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4395,12 +4435,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4425,33 +4465,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4468,12 +4508,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4498,33 +4538,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 39,7%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4541,12 +4581,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4571,33 +4611,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4614,12 +4654,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4644,7 +4684,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 412,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4653,24 +4693,24 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>58</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4687,12 +4727,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4717,7 +4757,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 236,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4726,24 +4766,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 3600,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4760,12 +4800,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4790,7 +4830,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4798,10 +4838,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4810,39 +4848,37 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4870,17 +4906,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4910,12 +4946,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4951,9 +4987,9 @@
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4983,12 +5019,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5013,33 +5049,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
         <is>
           <t>▲ 100,0%</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 255,6%</t>
-        </is>
-      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5056,12 +5092,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5095,11 +5131,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5117,7 +5153,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5129,12 +5165,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5159,7 +5195,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5168,16 +5204,16 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5202,12 +5238,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5243,9 +5279,9 @@
       <c r="I65" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5275,12 +5311,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5316,9 +5352,9 @@
       <c r="I66" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5348,12 +5384,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5387,7 +5423,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5421,12 +5457,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5454,17 +5490,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5494,12 +5530,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5567,12 +5603,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5597,33 +5633,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 280,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5640,12 +5676,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5713,12 +5749,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5743,33 +5779,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
+          <t>R$ 177,00</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5786,12 +5822,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5827,9 +5863,9 @@
       <c r="I73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5859,12 +5895,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5889,33 +5925,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>6</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5932,12 +5968,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5962,55 +5998,59 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6035,7 +6075,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6044,24 +6084,24 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2700,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6078,12 +6118,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6108,7 +6148,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6117,24 +6157,24 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6151,12 +6191,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6190,11 +6230,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,9%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6224,12 +6264,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6263,11 +6303,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6297,12 +6337,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6327,7 +6367,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6336,16 +6376,16 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
@@ -6353,7 +6393,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6370,12 +6410,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6409,11 +6449,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6443,12 +6483,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6476,17 +6516,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6516,12 +6556,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6546,7 +6586,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6554,8 +6594,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>1</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6564,37 +6606,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6619,33 +6663,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6662,12 +6706,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6703,9 +6747,9 @@
       <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6735,12 +6779,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6765,33 +6809,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>32</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 255,6%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6808,12 +6852,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6847,11 +6891,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6869,7 +6913,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6881,12 +6925,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6911,33 +6955,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 172,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 89,9%</t>
+        <v>9</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6954,12 +6998,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6995,9 +7039,9 @@
       <c r="I89" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7027,12 +7071,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7057,33 +7101,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 516,00</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 125,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 52,2%</t>
+        <v>3</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7100,12 +7144,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7139,7 +7183,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7161,7 +7205,7 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -7173,12 +7217,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7203,33 +7247,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>414</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 107,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7246,12 +7290,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7276,7 +7320,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7284,51 +7328,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7353,25 +7393,25 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 344,00</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 280,00</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,1%</t>
+        <v>5</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
@@ -7379,7 +7419,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7396,12 +7436,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7426,7 +7466,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7434,51 +7474,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7503,33 +7539,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
+          <t>R$ 210,00</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,4%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>213</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,5%</t>
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7546,12 +7582,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7576,7 +7612,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7584,51 +7620,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7653,33 +7685,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>137</v>
+        <v>8</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▼ 38,3%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7696,12 +7728,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7726,59 +7758,55 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7803,33 +7831,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 401,00</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,6%</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,3%</t>
+          <t>▲ 2700,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7846,12 +7874,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7876,7 +7904,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7884,51 +7912,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I101" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7953,33 +7977,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 387,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7996,82 +8020,1854 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 172,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 89,9%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 516,00</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 125,3%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 52,2%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,4%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>414</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 107,0%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 344,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,1%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,4%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,5%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,3%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 401,00</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,6%</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,3%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-032</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Petala Jasmin -1730</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 387,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>4533595417</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,90</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
+++ b/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,55 +666,59 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -816,7 +820,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -824,47 +828,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -966,55 +974,59 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1086,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1116,55 +1128,59 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1236,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1266,7 +1282,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1275,24 +1291,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 61,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1309,12 +1325,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1386,12 +1402,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1419,17 +1435,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1459,12 +1475,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1536,12 +1552,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1566,7 +1582,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1575,24 +1591,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 72,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1609,12 +1625,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1686,12 +1702,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1725,11 +1741,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 81,2%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1759,12 +1775,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1836,12 +1852,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1871,20 +1887,20 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,7%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -1892,7 +1908,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1909,12 +1925,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1986,12 +2002,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2016,33 +2032,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+        <v>12</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2059,12 +2075,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2089,7 +2105,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2097,8 +2113,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2107,37 +2125,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2162,33 +2182,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>18</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2205,12 +2225,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2282,12 +2302,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2312,33 +2332,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▲ 57,1%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2355,12 +2375,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2432,12 +2452,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2465,22 +2485,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,7%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -2488,7 +2508,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2505,12 +2525,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2582,12 +2602,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2612,33 +2632,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2655,12 +2675,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2732,12 +2752,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2762,33 +2782,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2805,12 +2825,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2882,12 +2902,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2912,33 +2932,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 68,4%</t>
+          <t>▼ 25,9%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2955,12 +2975,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2985,7 +3005,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2993,8 +3013,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3003,37 +3025,39 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3058,33 +3082,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,6%</t>
+        <v>27</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3101,12 +3125,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3178,12 +3202,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3208,33 +3232,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3251,12 +3275,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3328,12 +3352,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3358,33 +3382,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3401,12 +3425,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3478,12 +3502,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3508,7 +3532,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3517,24 +3541,24 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3551,12 +3575,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3628,12 +3652,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3667,11 +3691,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3701,12 +3725,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3778,12 +3802,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3817,11 +3841,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3851,12 +3875,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3881,7 +3905,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3889,8 +3913,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3899,37 +3925,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3954,7 +3982,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3963,24 +3991,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3997,12 +4025,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4027,7 +4055,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4035,47 +4063,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4109,11 +4141,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▼ 55,6%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4143,12 +4175,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4173,7 +4205,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4181,47 +4213,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4249,22 +4285,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4272,7 +4308,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4289,12 +4325,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4319,55 +4355,59 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4392,33 +4432,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,7%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▼ 48,6%</t>
+          <t>▼ 61,5%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4435,12 +4475,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4465,7 +4505,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4473,47 +4513,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>3</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4538,33 +4582,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 39,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4581,12 +4625,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4611,55 +4655,59 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,9%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4684,7 +4732,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 412,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4693,24 +4741,24 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 2800,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4727,12 +4775,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4757,7 +4805,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 236,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4765,47 +4813,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3600,0%</t>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>4</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4833,17 +4885,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 81,2%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4873,12 +4925,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4903,7 +4955,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4911,47 +4963,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4976,33 +5032,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,7%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5019,12 +5075,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5049,55 +5105,59 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5122,7 +5182,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5131,24 +5191,24 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5165,12 +5225,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5195,7 +5255,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5204,24 +5264,24 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5238,12 +5298,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5271,17 +5331,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5311,12 +5371,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5341,7 +5401,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5349,47 +5409,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5414,33 +5478,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5457,12 +5521,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5487,7 +5551,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5495,47 +5559,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5560,33 +5628,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5603,12 +5671,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5633,55 +5701,59 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5706,33 +5778,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5749,12 +5821,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5779,55 +5851,59 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5852,33 +5928,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5895,12 +5971,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5925,55 +6001,59 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5998,59 +6078,55 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 68,4%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6075,7 +6151,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6084,24 +6160,24 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6118,12 +6194,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6148,33 +6224,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,6%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6191,12 +6267,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6221,55 +6297,59 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6294,33 +6374,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>27</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,8%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6337,12 +6417,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6367,7 +6447,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6375,47 +6455,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6440,7 +6524,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6449,24 +6533,24 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>26</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6483,12 +6567,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6513,7 +6597,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6521,47 +6605,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6586,7 +6674,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6594,10 +6682,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6606,39 +6692,37 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6663,55 +6747,59 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6747,9 +6835,9 @@
       <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6779,12 +6867,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6809,55 +6897,59 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 255,6%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6885,17 +6977,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6913,7 +7005,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6925,12 +7017,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6955,7 +7047,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6964,24 +7056,24 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6998,12 +7090,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7028,7 +7120,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7037,24 +7129,24 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7071,12 +7163,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7110,11 +7202,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7144,12 +7236,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7177,17 +7269,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7217,12 +7309,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7250,17 +7342,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7290,12 +7382,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7320,33 +7412,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7363,12 +7455,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7393,33 +7485,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 280,00</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7436,12 +7528,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7466,33 +7558,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>18</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 48,6%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7509,12 +7601,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7539,33 +7631,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7582,12 +7674,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7612,33 +7704,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 39,7%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7655,12 +7747,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7685,33 +7777,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7728,12 +7820,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7758,33 +7850,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 412,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>58</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7801,12 +7893,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7831,7 +7923,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
+          <t>R$ 236,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7840,24 +7932,24 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▲ 2700,0%</t>
+          <t>▲ 3600,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7874,12 +7966,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7904,7 +7996,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7915,22 +8007,22 @@
       <c r="I101" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7947,12 +8039,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7980,9 +8072,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
@@ -7990,7 +8082,7 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8020,12 +8112,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8059,11 +8151,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8093,12 +8185,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8123,33 +8215,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8166,12 +8258,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8239,12 +8331,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8269,33 +8361,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8312,12 +8404,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8373,7 +8465,7 @@
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
@@ -8385,12 +8477,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8415,7 +8507,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8424,24 +8516,24 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8458,12 +8550,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8499,9 +8591,9 @@
       <c r="I109" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8531,12 +8623,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8564,17 +8656,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8604,12 +8696,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8643,11 +8735,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8677,12 +8769,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8707,33 +8799,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 172,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▼ 89,9%</t>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8750,12 +8842,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8823,12 +8915,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8853,33 +8945,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 516,00</t>
+          <t>R$ 177,00</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>▲ 125,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 52,2%</t>
+        <v>20</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8896,12 +8988,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8957,7 +9049,7 @@
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
@@ -8969,12 +9061,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8999,33 +9091,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,4%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>414</v>
+        <v>6</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>▲ 107,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9042,12 +9134,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9119,12 +9211,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9149,33 +9241,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 344,00</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,1%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9192,12 +9284,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9222,7 +9314,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9230,10 +9322,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
@@ -9242,39 +9332,37 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9299,33 +9387,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>213</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,5%</t>
+        <v>3</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9342,12 +9430,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9372,7 +9460,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9380,51 +9468,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9449,33 +9533,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>▼ 38,3%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9492,12 +9576,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9522,7 +9606,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9530,10 +9614,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9542,39 +9624,37 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9599,33 +9679,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 401,00</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>222</v>
+        <v>6</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9642,12 +9722,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9719,12 +9799,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9749,33 +9829,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 387,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9792,82 +9872,3168 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 255,6%</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 280,00</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>80,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>75,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2700,0%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 172,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 89,9%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 516,00</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 125,3%</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 52,2%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,4%</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>414</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 107,0%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 344,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,1%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,4%</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,5%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,3%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 401,00</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,6%</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,3%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-032</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Petala Jasmin -1730</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 387,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>4533595417</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,90</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
+++ b/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,14 +636,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -666,7 +666,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -674,10 +674,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -686,39 +684,37 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +786,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +863,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +940,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1017,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1094,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1171,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,14 +1248,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1282,7 +1278,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1290,8 +1286,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1300,37 +1298,39 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1402,14 +1402,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1435,17 +1435,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1475,12 +1475,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1552,14 +1552,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1582,33 +1582,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 72,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1625,12 +1625,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1702,14 +1702,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1732,33 +1732,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 72,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1852,14 +1852,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1882,33 +1882,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2002,14 +2002,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2032,33 +2032,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>30</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2152,14 +2152,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2182,33 +2182,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2302,14 +2302,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2332,33 +2332,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2452,14 +2452,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2482,33 +2482,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,7%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2602,14 +2602,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2641,24 +2641,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,2%</t>
+        <v>16</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2675,12 +2675,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2752,14 +2752,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2791,11 +2791,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2902,14 +2902,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2941,11 +2941,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,9%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3052,14 +3052,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3091,11 +3091,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>20</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,9%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3125,12 +3125,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3202,14 +3202,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3241,11 +3241,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>27</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3352,14 +3352,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3385,17 +3385,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3502,14 +3502,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3532,33 +3532,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 57,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3575,12 +3575,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3652,14 +3652,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3691,24 +3691,24 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3802,14 +3802,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3835,17 +3835,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3952,14 +3952,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3982,33 +3982,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4025,12 +4025,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4102,14 +4102,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4132,33 +4132,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4252,14 +4252,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4282,33 +4282,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4402,14 +4402,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4437,20 +4437,20 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,5%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4475,12 +4475,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4552,14 +4552,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4591,24 +4591,24 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,5%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4702,14 +4702,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4741,11 +4741,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4852,14 +4852,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4885,17 +4885,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 81,2%</t>
+        <v>12</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5002,14 +5002,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5032,33 +5032,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 81,2%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5152,14 +5152,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5187,20 +5187,20 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▲ 6,7%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5225,14 +5225,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5263,8 +5263,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5273,39 +5275,41 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5328,33 +5332,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5371,14 +5375,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5401,7 +5405,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5409,10 +5413,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5421,41 +5423,39 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5478,33 +5478,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 57,1%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5598,14 +5598,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5631,22 +5631,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
@@ -5671,12 +5671,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5748,14 +5748,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5778,33 +5778,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5898,14 +5898,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5928,33 +5928,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6048,14 +6048,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6087,16 +6087,16 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 68,4%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6121,14 +6121,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6159,8 +6159,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6169,39 +6171,41 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6227,22 +6231,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▼ 29,6%</t>
+          <t>▼ 68,4%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
@@ -6267,14 +6271,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6297,7 +6301,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6305,10 +6309,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6317,41 +6319,39 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6374,33 +6374,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,8%</t>
+        <v>19</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,6%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6417,12 +6417,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6494,14 +6494,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6524,33 +6524,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▲ 3,8%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6644,14 +6644,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6683,24 +6683,24 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>26</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6794,14 +6794,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6833,11 +6833,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6944,14 +6944,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6977,17 +6977,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7017,14 +7017,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -7055,8 +7055,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
-        <v>0</v>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7065,39 +7067,41 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7120,33 +7124,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7163,12 +7167,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7204,9 +7208,9 @@
       <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7236,14 +7240,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7266,33 +7270,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7309,14 +7313,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7348,11 +7352,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7382,14 +7386,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7412,33 +7416,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7455,14 +7459,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7488,17 +7492,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7528,14 +7532,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7558,20 +7562,20 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>▼ 48,6%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7580,11 +7584,11 @@
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7601,14 +7605,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7631,33 +7635,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7674,14 +7678,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7704,33 +7708,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,0%</t>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>▼ 39,7%</t>
+          <t>▼ 48,6%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7747,14 +7751,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7777,33 +7781,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,9%</t>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7820,14 +7824,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7850,33 +7854,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 412,00</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>35</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 39,7%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7893,14 +7897,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7923,33 +7927,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 236,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3600,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7966,14 +7970,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7996,7 +8000,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 412,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -8005,24 +8009,24 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>58</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -8039,14 +8043,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8069,7 +8073,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 236,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8078,24 +8082,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>37</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3600,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8112,14 +8116,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8151,11 +8155,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8185,14 +8189,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8218,17 +8222,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8258,14 +8262,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8297,11 +8301,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8331,14 +8335,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8361,33 +8365,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8404,12 +8408,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8447,7 +8451,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8477,14 +8481,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8507,7 +8511,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8516,24 +8520,24 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8550,14 +8554,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8589,7 +8593,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -8623,14 +8627,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8662,11 +8666,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8696,12 +8700,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8737,9 +8741,9 @@
       <c r="I111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8769,14 +8773,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8802,17 +8806,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8842,14 +8846,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8881,11 +8885,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8915,14 +8919,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8945,33 +8949,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8988,12 +8992,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9031,7 +9035,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9061,14 +9065,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9091,25 +9095,25 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 177,00</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
@@ -9117,7 +9121,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9134,14 +9138,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9164,7 +9168,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9172,10 +9176,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
@@ -9184,41 +9186,39 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9241,33 +9241,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9284,14 +9284,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9322,8 +9322,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="2" t="n">
-        <v>0</v>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
@@ -9332,39 +9334,41 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9387,33 +9391,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9430,12 +9434,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9471,9 +9475,9 @@
       <c r="I121" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9503,14 +9507,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9533,33 +9537,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9576,14 +9580,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9615,11 +9619,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9649,14 +9653,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9679,7 +9683,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9688,24 +9692,24 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9722,14 +9726,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9752,7 +9756,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9760,10 +9764,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -9772,41 +9774,39 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9832,17 +9832,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9872,14 +9872,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9910,8 +9910,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="n">
-        <v>0</v>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9920,39 +9922,41 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9975,33 +9979,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 255,6%</t>
+        <v>4</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10018,12 +10022,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10059,9 +10063,9 @@
       <c r="I129" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10079,7 +10083,7 @@
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
@@ -10091,14 +10095,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10121,25 +10125,25 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 255,6%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
@@ -10147,7 +10151,7 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10164,14 +10168,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10203,11 +10207,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10225,7 +10229,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -10237,14 +10241,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10267,7 +10271,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10276,24 +10280,24 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10310,14 +10314,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10349,11 +10353,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10383,14 +10387,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10416,17 +10420,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10456,14 +10460,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10495,11 +10499,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10529,14 +10533,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10559,33 +10563,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 280,00</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10602,14 +10606,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10641,11 +10645,11 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10675,14 +10679,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10705,33 +10709,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
+          <t>R$ 280,00</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>80,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10748,12 +10752,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10789,9 +10793,9 @@
       <c r="I139" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10821,14 +10825,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10851,33 +10855,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="inlineStr">
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
-      <c r="I140" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
-        </is>
-      </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10894,14 +10898,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10927,17 +10931,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10967,14 +10971,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10997,33 +11001,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2700,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11040,14 +11044,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11070,33 +11074,33 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -11113,14 +11117,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11143,33 +11147,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
+        <v>28</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2700,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11186,14 +11190,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11216,7 +11220,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11225,24 +11229,24 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11259,14 +11263,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11289,33 +11293,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11332,12 +11336,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11405,14 +11409,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11435,33 +11439,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11478,12 +11482,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11521,7 +11525,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11539,7 +11543,7 @@
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
@@ -11551,14 +11555,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11581,33 +11585,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11624,14 +11628,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11663,11 +11667,11 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11685,7 +11689,7 @@
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -11697,14 +11701,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11727,33 +11731,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11770,14 +11774,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11809,11 +11813,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11843,14 +11847,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11873,33 +11877,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 172,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>▼ 89,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11916,14 +11920,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11955,11 +11959,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11989,14 +11993,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12019,33 +12023,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 516,00</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 125,3%</t>
+          <t>R$ 172,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>▼ 52,2%</t>
+          <t>▼ 89,9%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12062,12 +12066,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12105,7 +12109,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12123,7 +12127,7 @@
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
@@ -12135,14 +12139,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12165,33 +12169,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,4%</t>
+          <t>R$ 516,00</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 125,3%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>414</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 107,0%</t>
+        <v>198</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 52,2%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12208,14 +12212,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12238,7 +12242,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12246,10 +12250,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I159" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12258,41 +12260,39 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12315,25 +12315,25 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 344,00</t>
+          <t>R$ 229,00</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,1%</t>
+        <v>414</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 107,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12358,12 +12358,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12435,14 +12435,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12465,33 +12465,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,4%</t>
+          <t>R$ 344,00</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>213</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 55,5%</t>
+        <v>200</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12508,12 +12508,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12585,14 +12585,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12615,33 +12615,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,4%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,3%</t>
+        <v>213</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 55,5%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12735,14 +12735,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12765,33 +12765,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 401,00</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,6%</t>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>222</v>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,3%</t>
+        <v>137</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,3%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12885,14 +12885,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12915,20 +12915,20 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 387,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 401,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,6%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>222</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,3%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12958,82 +12958,232 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-032</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Petala Jasmin -1730</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 387,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>4533595417</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,90</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
+++ b/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,14 +636,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,14 +786,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -816,7 +816,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -824,10 +824,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -836,39 +834,37 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -940,12 +936,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1017,12 +1013,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1094,12 +1090,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1171,12 +1167,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1248,12 +1244,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1325,12 +1321,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1402,14 +1398,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1432,7 +1428,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1440,8 +1436,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1450,37 +1448,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1552,14 +1552,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1585,17 +1585,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1625,12 +1625,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1702,14 +1702,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1732,33 +1732,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 72,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1852,14 +1852,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1882,33 +1882,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 72,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2002,14 +2002,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2032,33 +2032,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2152,14 +2152,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2182,33 +2182,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2302,14 +2302,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2332,33 +2332,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2452,14 +2452,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2482,33 +2482,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2602,14 +2602,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2632,33 +2632,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2675,12 +2675,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2752,14 +2752,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2791,24 +2791,24 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,2%</t>
+          <t>▲ 6,7%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2902,14 +2902,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2941,11 +2941,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3052,14 +3052,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3091,11 +3091,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,9%</t>
+        <v>16</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3125,12 +3125,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3202,14 +3202,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3241,11 +3241,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>20</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,9%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3352,14 +3352,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3391,11 +3391,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>27</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3502,14 +3502,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3535,17 +3535,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3575,12 +3575,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3652,14 +3652,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3682,33 +3682,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 57,1%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3802,14 +3802,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3841,24 +3841,24 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3952,14 +3952,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3985,17 +3985,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -4025,12 +4025,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4102,14 +4102,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4132,33 +4132,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4252,14 +4252,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4282,33 +4282,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4402,14 +4402,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4432,33 +4432,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4475,12 +4475,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4552,14 +4552,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4587,20 +4587,20 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 61,5%</t>
+        <v>4</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4702,14 +4702,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4741,24 +4741,24 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 61,5%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4852,14 +4852,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4891,11 +4891,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5002,14 +5002,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5035,17 +5035,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 81,2%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5152,14 +5152,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5182,33 +5182,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,7%</t>
+          <t>▼ 81,2%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5302,14 +5302,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5337,20 +5337,20 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+        <v>16</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,7%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5375,14 +5375,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5413,8 +5413,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5423,39 +5425,41 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5478,33 +5482,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>15</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5521,14 +5525,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5551,7 +5555,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5559,10 +5563,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5571,41 +5573,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5628,33 +5628,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 57,1%</t>
+        <v>13</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5748,14 +5748,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5781,22 +5781,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
@@ -5821,12 +5821,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5898,14 +5898,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5928,33 +5928,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6048,14 +6048,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6078,33 +6078,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6198,14 +6198,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6237,16 +6237,16 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 68,4%</t>
+        <v>4</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6271,14 +6271,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6309,8 +6309,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6319,39 +6321,41 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6377,22 +6381,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,6%</t>
+        <v>6</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 68,4%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
@@ -6417,14 +6421,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6447,7 +6451,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6455,10 +6459,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6467,41 +6469,39 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6524,33 +6524,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,8%</t>
+          <t>▼ 29,6%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6644,14 +6644,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6674,33 +6674,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>27</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,8%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6794,14 +6794,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6833,24 +6833,24 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>26</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6944,14 +6944,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6983,11 +6983,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7094,14 +7094,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7127,17 +7127,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7167,14 +7167,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7205,8 +7205,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>0</v>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7215,39 +7217,41 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7270,33 +7274,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7313,12 +7317,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7354,9 +7358,9 @@
       <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7386,14 +7390,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7416,33 +7420,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7459,14 +7463,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7498,11 +7502,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7532,14 +7536,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7562,33 +7566,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7605,14 +7609,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7638,17 +7642,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7678,14 +7682,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7708,20 +7712,20 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,7%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 48,6%</t>
+        <v>9</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7730,11 +7734,11 @@
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7751,14 +7755,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7781,33 +7785,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7824,14 +7828,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7854,33 +7858,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 39,7%</t>
+        <v>18</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▼ 48,6%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7897,14 +7901,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7927,33 +7931,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,9%</t>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7970,14 +7974,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8000,33 +8004,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 412,00</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>▲ 2800,0%</t>
+          <t>▼ 39,7%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -8043,14 +8047,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8073,33 +8077,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 236,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>▲ 3600,0%</t>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8116,14 +8120,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8146,7 +8150,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 412,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8155,24 +8159,24 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>58</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8189,14 +8193,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8219,7 +8223,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 236,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8228,24 +8232,24 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 3600,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8262,14 +8266,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8301,11 +8305,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8335,14 +8339,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8368,17 +8372,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8408,14 +8412,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8447,11 +8451,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8481,14 +8485,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8511,33 +8515,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8554,12 +8558,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8597,7 +8601,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8627,14 +8631,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8657,7 +8661,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8666,24 +8670,24 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8700,14 +8704,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8739,7 +8743,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8773,14 +8777,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8812,11 +8816,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8846,12 +8850,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8887,9 +8891,9 @@
       <c r="I113" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8919,14 +8923,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8952,17 +8956,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>▼ 90,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8992,14 +8996,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9031,11 +9035,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9065,14 +9069,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9095,33 +9099,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>▲ 233,3%</t>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9138,12 +9142,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9181,7 +9185,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9211,14 +9215,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9241,25 +9245,25 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
@@ -9267,7 +9271,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9284,14 +9288,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9314,7 +9318,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9322,10 +9326,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
@@ -9334,41 +9336,39 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9391,33 +9391,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9434,14 +9434,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9472,8 +9472,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="n">
-        <v>0</v>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9482,39 +9484,41 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9537,33 +9541,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9580,12 +9584,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9621,9 +9625,9 @@
       <c r="I123" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9653,14 +9657,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9683,33 +9687,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9726,14 +9730,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9765,11 +9769,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9799,14 +9803,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9829,7 +9833,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9838,24 +9842,24 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9872,14 +9876,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9902,7 +9906,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9910,10 +9914,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I127" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9922,41 +9924,39 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9982,17 +9982,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -10022,14 +10022,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -10060,8 +10060,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="n">
-        <v>0</v>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -10070,39 +10072,41 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10125,33 +10129,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>▲ 255,6%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10168,12 +10172,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10209,9 +10213,9 @@
       <c r="I131" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10229,7 +10233,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -10241,14 +10245,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10271,25 +10275,25 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J132" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>32</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▲ 255,6%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
@@ -10297,7 +10301,7 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10314,14 +10318,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10353,11 +10357,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10375,7 +10379,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -10387,14 +10391,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10417,7 +10421,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10426,24 +10430,24 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10460,14 +10464,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10499,11 +10503,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10533,14 +10537,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10566,17 +10570,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10606,14 +10610,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10645,11 +10649,11 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10679,14 +10683,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10709,33 +10713,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 280,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10752,14 +10756,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10791,11 +10795,11 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10825,14 +10829,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10855,33 +10859,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 280,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>80,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10898,12 +10902,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10939,9 +10943,9 @@
       <c r="I141" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10971,14 +10975,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11001,33 +11005,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 210,00</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
-      <c r="I142" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
-        </is>
-      </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11044,14 +11048,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11077,17 +11081,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11117,14 +11121,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11147,33 +11151,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>▲ 2700,0%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11190,14 +11194,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11220,33 +11224,33 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11263,14 +11267,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11293,33 +11297,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,9%</t>
+          <t>▲ 2700,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11336,14 +11340,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11366,7 +11370,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11375,24 +11379,24 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K147" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11409,14 +11413,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11439,33 +11443,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11482,12 +11486,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11555,14 +11559,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11585,33 +11589,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11628,12 +11632,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11671,7 +11675,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11689,7 +11693,7 @@
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -11701,14 +11705,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11731,33 +11735,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11774,14 +11778,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11813,11 +11817,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11835,7 +11839,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -11847,14 +11851,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11877,33 +11881,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11920,14 +11924,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11959,11 +11963,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11993,14 +11997,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12023,33 +12027,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 172,00</t>
-        </is>
-      </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 89,9%</t>
+        <v>10</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12066,14 +12070,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12105,11 +12109,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12139,14 +12143,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12169,33 +12173,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 516,00</t>
+          <t>R$ 172,00</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>▲ 125,3%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 52,2%</t>
+        <v>20</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▼ 89,9%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12212,12 +12216,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12255,7 +12259,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12273,7 +12277,7 @@
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
@@ -12285,14 +12289,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12315,33 +12319,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
+          <t>R$ 516,00</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,4%</t>
+          <t>▲ 125,3%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>414</v>
+        <v>198</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▲ 107,0%</t>
+          <t>▼ 52,2%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12358,14 +12362,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12388,7 +12392,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12396,10 +12400,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I161" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -12408,41 +12410,39 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12465,25 +12465,25 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 344,00</t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,1%</t>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>200</v>
+        <v>414</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,1%</t>
+          <t>▲ 107,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12508,12 +12508,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12585,14 +12585,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12615,33 +12615,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
+          <t>R$ 344,00</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,4%</t>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 55,5%</t>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12735,14 +12735,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12765,33 +12765,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
+          <t>R$ 459,00</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▲ 100,4%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>▼ 38,3%</t>
+          <t>▲ 55,5%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12885,14 +12885,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12915,33 +12915,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 401,00</t>
+          <t>R$ 229,00</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,6%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>222</v>
+        <v>137</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>▲ 2,3%</t>
+          <t>▼ 38,3%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13035,14 +13035,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -13065,20 +13065,20 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 387,00</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 401,00</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,6%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>222</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,3%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13108,82 +13108,232 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-032</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Petala Jasmin -1730</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 387,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>4533595417</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,90</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
+++ b/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,14 +636,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -666,7 +666,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -675,24 +675,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▲ 275,0%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,14 +786,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,14 +936,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -966,7 +966,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -974,10 +974,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -986,39 +984,37 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1090,12 +1086,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1167,12 +1163,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1244,12 +1240,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1321,12 +1317,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1398,12 +1394,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1475,12 +1471,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1552,14 +1548,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1582,7 +1578,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1590,8 +1586,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1600,37 +1598,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1702,14 +1702,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1735,17 +1735,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1852,14 +1852,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -1882,33 +1882,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▼ 72,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2002,14 +2002,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2032,33 +2032,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 72,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2152,14 +2152,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2182,33 +2182,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2302,14 +2302,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2332,33 +2332,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>30</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2452,14 +2452,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2482,33 +2482,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2602,14 +2602,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2632,33 +2632,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2675,12 +2675,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2752,14 +2752,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2782,33 +2782,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,7%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2902,14 +2902,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2941,24 +2941,24 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,2%</t>
+        <v>16</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,7%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3052,14 +3052,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3091,11 +3091,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3125,12 +3125,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3202,14 +3202,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3241,11 +3241,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,9%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3352,14 +3352,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3391,11 +3391,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>20</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,9%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3502,14 +3502,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3541,11 +3541,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>27</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3575,12 +3575,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3652,14 +3652,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3685,17 +3685,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3802,14 +3802,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3832,33 +3832,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 57,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3952,14 +3952,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3991,24 +3991,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4025,12 +4025,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4102,14 +4102,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4135,17 +4135,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4252,14 +4252,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4282,33 +4282,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4402,14 +4402,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4432,33 +4432,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4475,12 +4475,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4552,14 +4552,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4582,33 +4582,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4702,14 +4702,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4737,20 +4737,20 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▼ 61,5%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4852,14 +4852,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4891,24 +4891,24 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 61,5%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5002,14 +5002,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5041,11 +5041,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5152,14 +5152,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5185,17 +5185,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 81,2%</t>
+        <v>12</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5302,14 +5302,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5332,33 +5332,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 81,2%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5375,12 +5375,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5452,14 +5452,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5487,20 +5487,20 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▲ 6,7%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5525,14 +5525,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5563,8 +5563,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5573,39 +5575,41 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5628,33 +5632,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5671,14 +5675,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5701,7 +5705,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5709,10 +5713,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5721,41 +5723,39 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5778,33 +5778,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▲ 57,1%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5898,14 +5898,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -5931,22 +5931,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
@@ -5971,12 +5971,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6048,14 +6048,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6078,33 +6078,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6198,14 +6198,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6228,33 +6228,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6348,14 +6348,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6387,16 +6387,16 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>▼ 68,4%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6421,14 +6421,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6459,8 +6459,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6469,39 +6471,41 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6527,22 +6531,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▼ 29,6%</t>
+          <t>▼ 68,4%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6567,14 +6571,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6597,7 +6601,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6605,10 +6609,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6617,41 +6619,39 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6674,33 +6674,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3,8%</t>
+        <v>19</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 29,6%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6794,14 +6794,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6824,33 +6824,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▲ 73,3%</t>
+          <t>▲ 3,8%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6944,14 +6944,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6983,24 +6983,24 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>26</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7094,14 +7094,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7133,11 +7133,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7167,12 +7167,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7244,14 +7244,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7277,17 +7277,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="4" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7317,14 +7317,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7355,8 +7355,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="n">
-        <v>0</v>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7365,39 +7367,41 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7420,33 +7424,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7463,12 +7467,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7504,9 +7508,9 @@
       <c r="I94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7536,14 +7540,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7566,33 +7570,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7609,14 +7613,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7648,11 +7652,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7682,14 +7686,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7712,33 +7716,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7755,14 +7759,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7788,17 +7792,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7828,14 +7832,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7858,20 +7862,20 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>▼ 48,6%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7880,11 +7884,11 @@
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7901,14 +7905,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -7931,33 +7935,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7974,14 +7978,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8004,33 +8008,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>▼ 57,0%</t>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>▼ 39,7%</t>
+          <t>▼ 48,6%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -8047,14 +8051,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8077,33 +8081,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▼ 91,9%</t>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8120,14 +8124,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8150,33 +8154,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 412,00</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>35</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▼ 39,7%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8193,14 +8197,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8223,33 +8227,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 236,00</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3600,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8266,14 +8270,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8296,7 +8300,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 412,00</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8305,24 +8309,24 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>58</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8339,14 +8343,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8369,7 +8373,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 236,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8378,24 +8382,24 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>37</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3600,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8412,14 +8416,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8451,11 +8455,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8485,14 +8489,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8518,17 +8522,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8558,14 +8562,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8597,11 +8601,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8631,14 +8635,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8661,33 +8665,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8704,12 +8708,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8747,7 +8751,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8777,14 +8781,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8807,7 +8811,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8816,24 +8820,24 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8850,14 +8854,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8889,7 +8893,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -8923,14 +8927,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -8962,11 +8966,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8996,12 +9000,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9037,9 +9041,9 @@
       <c r="I115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9069,14 +9073,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9102,17 +9106,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▼ 90,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9142,14 +9146,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9181,11 +9185,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9215,14 +9219,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9245,33 +9249,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9288,12 +9292,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9331,7 +9335,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9361,14 +9365,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9391,25 +9395,25 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 177,00</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
@@ -9417,7 +9421,7 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9434,14 +9438,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9464,7 +9468,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9472,10 +9476,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9484,41 +9486,39 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9541,33 +9541,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
-        </is>
-      </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9584,14 +9584,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9622,8 +9622,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="n">
-        <v>0</v>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9632,39 +9634,41 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9687,33 +9691,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9730,12 +9734,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9771,9 +9775,9 @@
       <c r="I125" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9803,14 +9807,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9833,33 +9837,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9876,14 +9880,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9915,11 +9919,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9949,14 +9953,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -9979,7 +9983,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -9988,24 +9992,24 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10022,14 +10026,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10052,7 +10056,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -10060,10 +10064,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -10072,41 +10074,39 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10132,17 +10132,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H130" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J130" s="4" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10172,14 +10172,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10210,8 +10210,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I131" s="2" t="n">
-        <v>0</v>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -10220,39 +10222,41 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10275,33 +10279,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▲ 255,6%</t>
+        <v>4</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10318,12 +10322,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10359,9 +10363,9 @@
       <c r="I133" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10379,7 +10383,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -10391,14 +10395,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10421,25 +10425,25 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 255,6%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
@@ -10447,7 +10451,7 @@
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10464,14 +10468,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10503,11 +10507,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10525,7 +10529,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -10537,14 +10541,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10567,7 +10571,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10576,24 +10580,24 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10610,14 +10614,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10649,11 +10653,11 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10683,14 +10687,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10716,17 +10720,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10756,14 +10760,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10795,11 +10799,11 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10829,14 +10833,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10859,33 +10863,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 280,00</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10902,14 +10906,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -10941,11 +10945,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10975,14 +10979,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11005,33 +11009,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
+          <t>R$ 280,00</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>80,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="L142" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11048,12 +11052,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11089,9 +11093,9 @@
       <c r="I143" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11121,14 +11125,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11151,33 +11155,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr">
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
-      <c r="I144" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
-        </is>
-      </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11194,14 +11198,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11227,17 +11231,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11267,14 +11271,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11297,33 +11301,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2700,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11340,14 +11344,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11370,33 +11374,33 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11413,14 +11417,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11443,33 +11447,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
+        <v>28</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2700,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11486,14 +11490,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11516,7 +11520,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11525,24 +11529,24 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11559,14 +11563,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11589,33 +11593,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11632,12 +11636,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11705,14 +11709,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11735,33 +11739,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11778,12 +11782,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11821,7 +11825,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11839,7 +11843,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -11851,14 +11855,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11881,33 +11885,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11924,14 +11928,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -11963,11 +11967,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11985,7 +11989,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -11997,14 +12001,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12027,33 +12031,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12070,14 +12074,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12109,11 +12113,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12143,14 +12147,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12173,33 +12177,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 172,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>▼ 89,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12216,14 +12220,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12255,11 +12259,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J159" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12289,14 +12293,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12319,33 +12323,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 516,00</t>
-        </is>
-      </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>▲ 125,3%</t>
+          <t>R$ 172,00</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▼ 52,2%</t>
+          <t>▼ 89,9%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12362,12 +12366,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12405,7 +12409,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12423,7 +12427,7 @@
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
@@ -12435,14 +12439,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12465,33 +12469,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,4%</t>
+          <t>R$ 516,00</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>▲ 125,3%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>414</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▲ 107,0%</t>
+        <v>198</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▼ 52,2%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12508,14 +12512,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12538,7 +12542,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12546,10 +12550,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I163" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -12558,41 +12560,39 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12615,25 +12615,25 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 344,00</t>
+          <t>R$ 229,00</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,1%</t>
+        <v>414</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▲ 107,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12735,14 +12735,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12765,33 +12765,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,4%</t>
+          <t>R$ 344,00</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>213</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▲ 55,5%</t>
+        <v>200</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12885,14 +12885,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -12915,33 +12915,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,4%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>▼ 38,3%</t>
+        <v>213</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▲ 55,5%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13035,14 +13035,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -13065,33 +13065,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 401,00</t>
-        </is>
-      </c>
-      <c r="H170" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3,6%</t>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>222</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2,3%</t>
+        <v>137</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>▼ 38,3%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13185,14 +13185,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-032</t>
@@ -13215,20 +13215,20 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 387,00</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 401,00</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,6%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>222</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,3%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13258,82 +13258,232 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-032</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Petala Jasmin -1730</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 387,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>4533595417</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
+++ b/saida_skus/SKU_UTD-032-BOLEIRA-PETALA-JASMIN-1730.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -675,24 +675,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -827,9 +827,9 @@
       <c r="I5" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 275,0%</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,12 +936,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -975,11 +975,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>17</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▲ 142,9%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1116,59 +1116,55 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 70,8%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1240,12 +1236,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1270,7 +1266,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1278,51 +1274,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I11" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1394,12 +1386,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1424,7 +1416,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1432,51 +1424,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1548,12 +1536,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1578,7 +1566,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1586,10 +1574,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1598,39 +1584,37 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1702,12 +1686,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1732,7 +1716,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1740,8 +1724,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1750,37 +1736,39 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1852,12 +1840,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1882,55 +1870,59 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2002,12 +1994,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2032,7 +2024,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2040,47 +2032,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 72,0%</t>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2152,12 +2148,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2182,55 +2178,59 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2341,24 +2341,24 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2491,11 +2491,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2641,16 +2641,16 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▼ 72,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2675,12 +2675,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2791,11 +2791,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2941,16 +2941,16 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,7%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3085,17 +3085,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,2%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3125,12 +3125,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3241,24 +3241,24 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3352,12 +3352,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3385,17 +3385,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,9%</t>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3541,24 +3541,24 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3575,12 +3575,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3691,11 +3691,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3991,24 +3991,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▲ 57,1%</t>
+        <v>20</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,9%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4025,12 +4025,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4141,11 +4141,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>27</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4285,17 +4285,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4432,33 +4432,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4475,12 +4475,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4582,33 +4582,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4702,12 +4702,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4732,33 +4732,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4882,33 +4882,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>▼ 61,5%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5041,24 +5041,24 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5185,17 +5185,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5332,33 +5332,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>▼ 81,2%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5375,12 +5375,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5452,12 +5452,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5487,20 +5487,20 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 61,5%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5641,24 +5641,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5713,8 +5713,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5723,37 +5725,39 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5781,17 +5785,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5821,12 +5825,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5898,12 +5902,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5928,33 +5932,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▲ 57,1%</t>
+        <v>3</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 81,2%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5971,12 +5975,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6048,12 +6052,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6081,22 +6085,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,7%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
@@ -6104,7 +6108,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6121,12 +6125,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6198,12 +6202,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6228,33 +6232,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6271,12 +6275,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6301,7 +6305,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6309,10 +6313,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6321,39 +6323,37 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6378,33 +6378,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6421,12 +6421,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6537,16 +6537,16 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 68,4%</t>
+        <v>11</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6609,8 +6609,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>0</v>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6619,37 +6621,39 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6683,16 +6687,16 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▼ 29,6%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -6700,7 +6704,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6717,12 +6721,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6794,12 +6798,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6833,16 +6837,16 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,8%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
@@ -6850,7 +6854,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6867,12 +6871,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6944,12 +6948,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6979,20 +6983,20 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▲ 73,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
@@ -7017,12 +7021,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7094,12 +7098,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7124,33 +7128,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▼ 68,4%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7167,12 +7171,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7197,7 +7201,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7205,10 +7209,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7217,39 +7219,37 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7274,33 +7274,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 29,6%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7317,12 +7317,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7424,33 +7424,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▲ 3,8%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7505,8 +7505,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7515,37 +7517,39 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7579,16 +7583,16 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>26</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▲ 73,3%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
@@ -7596,7 +7600,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7613,12 +7617,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7643,7 +7647,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7651,47 +7655,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7719,17 +7727,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+        <v>15</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7759,12 +7767,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7789,7 +7797,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7797,47 +7805,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7862,33 +7874,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7905,12 +7917,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7935,55 +7947,59 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8008,33 +8024,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>▼ 48,6%</t>
+        <v>7</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -8051,12 +8067,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8081,7 +8097,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8090,24 +8106,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8124,12 +8140,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8154,33 +8170,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>▼ 39,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8197,12 +8213,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8230,17 +8246,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H104" s="4" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8270,12 +8286,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8300,33 +8316,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 412,00</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2800,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8343,12 +8359,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8373,7 +8389,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 236,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8382,24 +8398,24 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>▲ 3600,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8416,12 +8432,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8446,33 +8462,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8489,12 +8505,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8522,9 +8538,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
@@ -8532,7 +8548,7 @@
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8562,12 +8578,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8592,33 +8608,33 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,7%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 48,6%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8635,12 +8651,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8665,33 +8681,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8708,12 +8724,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8738,33 +8754,33 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,0%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>35</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▼ 39,7%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8781,12 +8797,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8811,33 +8827,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8854,12 +8870,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8884,7 +8900,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 412,00</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -8893,24 +8909,24 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>58</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2800,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8927,12 +8943,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8957,7 +8973,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 236,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8966,24 +8982,24 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>37</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3600,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9000,12 +9016,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9039,7 +9055,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -9073,12 +9089,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9112,11 +9128,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9146,12 +9162,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9219,12 +9235,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9260,9 +9276,9 @@
       <c r="I118" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▼ 90,0%</t>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9292,12 +9308,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9365,12 +9381,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9395,33 +9411,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 177,00</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9438,12 +9454,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9511,12 +9527,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9541,33 +9557,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9584,12 +9600,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9614,7 +9630,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9622,10 +9638,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9634,39 +9648,37 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9691,7 +9703,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9700,24 +9712,24 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9734,12 +9746,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9775,9 +9787,9 @@
       <c r="I125" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9807,12 +9819,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9846,11 +9858,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 90,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9880,12 +9892,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9919,11 +9931,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9953,12 +9965,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9983,33 +9995,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 177,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10026,12 +10038,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10065,7 +10077,7 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -10099,12 +10111,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10129,12 +10141,12 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
@@ -10142,20 +10154,20 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10172,12 +10184,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10249,12 +10261,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10279,33 +10291,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10322,12 +10334,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10395,12 +10407,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10425,33 +10437,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▲ 255,6%</t>
+        <v>3</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10468,12 +10480,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10529,7 +10541,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -10541,12 +10553,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10571,7 +10583,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10580,16 +10592,16 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
@@ -10614,12 +10626,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10653,11 +10665,11 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10687,12 +10699,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10726,11 +10738,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10760,12 +10772,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10790,7 +10802,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -10798,8 +10810,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" s="2" t="n">
-        <v>2</v>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -10808,37 +10822,39 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10872,11 +10888,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10906,12 +10922,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10947,9 +10963,9 @@
       <c r="I141" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10979,12 +10995,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11009,33 +11025,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 280,00</t>
+          <t>R$ 140,00</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 255,6%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11052,12 +11068,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11091,11 +11107,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11113,7 +11129,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
@@ -11125,12 +11141,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11155,33 +11171,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="inlineStr">
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
         <is>
           <t>▲ 200,0%</t>
         </is>
       </c>
-      <c r="I144" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11198,12 +11214,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11271,12 +11287,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11301,33 +11317,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>3</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11344,12 +11360,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11377,9 +11393,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H147" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
@@ -11387,7 +11403,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11417,12 +11433,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11447,33 +11463,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2700,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11490,12 +11506,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11520,7 +11536,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11529,24 +11545,24 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11563,12 +11579,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11593,33 +11609,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 280,00</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
+        <v>5</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11636,12 +11652,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11709,12 +11725,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11739,33 +11755,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11782,12 +11798,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11823,9 +11839,9 @@
       <c r="I153" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11855,12 +11871,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11885,33 +11901,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11928,12 +11944,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11961,17 +11977,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11989,7 +12005,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -12001,12 +12017,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12031,7 +12047,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
+          <t>R$ 140,00</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -12040,24 +12056,24 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>28</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2700,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12074,12 +12090,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12104,7 +12120,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12113,24 +12129,24 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -12147,12 +12163,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12186,11 +12202,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12220,12 +12236,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12259,11 +12275,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12293,12 +12309,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12323,33 +12339,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 172,00</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▼ 89,9%</t>
+        <v>9</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12366,12 +12382,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12439,12 +12455,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12469,33 +12485,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 516,00</t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>▲ 125,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>198</v>
+        <v>6</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>▼ 52,2%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12512,12 +12528,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12585,12 +12601,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12615,33 +12631,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,4%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>414</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▲ 107,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12658,12 +12674,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12688,7 +12704,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12696,51 +12712,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12765,33 +12777,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 344,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,1%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12808,12 +12820,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12838,7 +12850,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12846,51 +12858,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I167" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12915,33 +12923,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 459,00</t>
-        </is>
-      </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,4%</t>
+          <t>R$ 172,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>213</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▲ 55,5%</t>
+        <v>20</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▼ 89,9%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12958,12 +12966,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -12988,7 +12996,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -12996,51 +13004,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I169" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13065,33 +13069,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 229,00</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+          <t>R$ 516,00</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>▲ 125,3%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
-          <t>▼ 38,3%</t>
+          <t>▼ 52,2%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13108,12 +13112,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13138,7 +13142,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -13146,10 +13150,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I171" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
@@ -13158,39 +13160,37 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13215,33 +13215,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 401,00</t>
-        </is>
-      </c>
-      <c r="H172" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3,6%</t>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,4%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>222</v>
+        <v>414</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>▲ 2,3%</t>
+          <t>▲ 107,0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13335,12 +13335,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13365,33 +13365,33 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>R$ 387,00</t>
-        </is>
-      </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 344,00</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,1%</t>
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>200</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,1%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L174" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -13408,82 +13408,682 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 459,00</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,4%</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="J176" s="3" t="inlineStr">
+        <is>
+          <t>▲ 55,5%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 229,00</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>▼ 38,3%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 401,00</t>
+        </is>
+      </c>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,6%</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,3%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4533595417</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-032</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Petala Jasmin -1730</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>4533595421</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 387,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-032</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Petala Jasmin -1730</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4533595417</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>